--- a/src/generated_files/MusicBrainz_Picard_Tag_Map.xlsx
+++ b/src/generated_files/MusicBrainz_Picard_Tag_Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="435">
   <si>
     <t xml:space="preserve">Tag Name</t>
   </si>
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Album Artist</t>
   </si>
   <si>
-    <t xml:space="preserve">albumartist</t>
+    <t xml:space="preserve">album_artist</t>
   </si>
   <si>
     <t xml:space="preserve">TPE2</t>
@@ -246,10 +246,10 @@
     <t xml:space="preserve">Comment [4]</t>
   </si>
   <si>
-    <t xml:space="preserve">comment:description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMM:description</t>
+    <t xml:space="preserve">comment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMM</t>
   </si>
   <si>
     <t xml:space="preserve">©cmt</t>
@@ -352,7 +352,7 @@
     <t xml:space="preserve">Disc Number</t>
   </si>
   <si>
-    <t xml:space="preserve">discnumber</t>
+    <t xml:space="preserve">disc</t>
   </si>
   <si>
     <t xml:space="preserve">TPOS</t>
@@ -893,6 +893,12 @@
     <t xml:space="preserve">originalyear</t>
   </si>
   <si>
+    <t xml:space="preserve">TORY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">----:com.apple.iTunes:originalyear</t>
+  </si>
+  <si>
     <t xml:space="preserve">WM/OriginalReleaseYear (Picard&gt;=1.3.1)</t>
   </si>
   <si>
@@ -955,7 +961,7 @@
     <t xml:space="preserve">Record Label</t>
   </si>
   <si>
-    <t xml:space="preserve">label</t>
+    <t xml:space="preserve">publisher</t>
   </si>
   <si>
     <t xml:space="preserve">TPUB</t>
@@ -1381,7 +1387,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1392,6 +1398,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE6E6E6"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00A933"/>
+        <bgColor rgb="FF008000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8000"/>
+        <bgColor rgb="FFFF6600"/>
       </patternFill>
     </fill>
   </fills>
@@ -1443,7 +1467,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1462,6 +1486,50 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1523,12 +1591,12 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF8000"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF00A933"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -1720,7 +1788,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E1048576"/>
+  <dimension ref="A1:XFD1048576"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="1" width="30.7"/>
@@ -1780,37 +1848,37 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    <row r="5" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="9" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1865,20 +1933,20 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="9" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="6" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1984,54 +2052,54 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+    <row r="16" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="9" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+    <row r="17" s="13" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="12" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+    <row r="18" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="9" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2069,20 +2137,20 @@
         <v>97</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+    <row r="21" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="9" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2103,20 +2171,20 @@
         <v>107</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+    <row r="23" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="9" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2205,20 +2273,20 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+    <row r="29" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="6" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2341,20 +2409,20 @@
         <v>173</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
+    <row r="37" s="13" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="12" t="s">
         <v>178</v>
       </c>
     </row>
@@ -2732,49 +2800,52 @@
         <v>280</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3" t="s">
+    <row r="60" s="14" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="E60" s="12" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="3" t="s">
+      <c r="XFB60" s="13"/>
+      <c r="XFC60" s="13"/>
+      <c r="XFD60" s="13"/>
+    </row>
+    <row r="61" s="13" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E61" s="4" t="s">
+      <c r="C61" s="12" t="s">
         <v>287</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>38</v>
@@ -2785,16 +2856,16 @@
     </row>
     <row r="63" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>38</v>
@@ -2802,16 +2873,16 @@
     </row>
     <row r="64" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>38</v>
@@ -2819,288 +2890,288 @@
     </row>
     <row r="65" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>38</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B67" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="C67" s="4" t="s">
+    </row>
+    <row r="67" s="13" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="B67" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="C67" s="12" t="s">
         <v>310</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B69" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="C69" s="4" t="s">
+    </row>
+    <row r="69" s="7" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="B69" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="C69" s="6" t="s">
         <v>320</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>38</v>
@@ -3108,16 +3179,16 @@
     </row>
     <row r="82" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>38</v>
@@ -3125,16 +3196,16 @@
     </row>
     <row r="83" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>38</v>
@@ -3142,149 +3213,155 @@
     </row>
     <row r="84" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="B85" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="C85" s="4" t="s">
+    </row>
+    <row r="85" s="15" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="C85" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D85" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="E85" s="4" t="s">
-        <v>393</v>
-      </c>
+      <c r="E85" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="XFB85" s="10"/>
+      <c r="XFC85" s="10"/>
+      <c r="XFD85" s="10"/>
     </row>
     <row r="86" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="3" t="s">
+    <row r="87" s="15" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="C87" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="D87" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="B88" s="4" t="s">
+      <c r="E87" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="XFB87" s="10"/>
+      <c r="XFC87" s="10"/>
+      <c r="XFD87" s="10"/>
+    </row>
+    <row r="88" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="B88" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="E88" s="4" t="s">
+      <c r="C88" s="6" t="s">
         <v>405</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>38</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>38</v>
@@ -3294,53 +3371,53 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="5" t="s">
-        <v>423</v>
+      <c r="B94" s="16" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/src/generated_files/MusicBrainz_Picard_Tag_Map.xlsx
+++ b/src/generated_files/MusicBrainz_Picard_Tag_Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="444">
   <si>
     <t xml:space="preserve">Tag Name</t>
   </si>
@@ -28,13 +28,22 @@
     <t xml:space="preserve">Internal Name</t>
   </si>
   <si>
-    <t xml:space="preserve">ID3v2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iTunes MP4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASF/Windows Media</t>
+    <t xml:space="preserve">ID3v2 (mp3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID3v2 datatype</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iTunes MP4 (m4a)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MP4 datatype</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASF/Windows Media (wma)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASF datatype</t>
   </si>
   <si>
     <t xml:space="preserve">AcoustID</t>
@@ -74,6 +83,9 @@
   </si>
   <si>
     <t xml:space="preserve">TALB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
   </si>
   <si>
     <t xml:space="preserve">©alb</t>
@@ -270,6 +282,9 @@
     <t xml:space="preserve">cpil</t>
   </si>
   <si>
+    <t xml:space="preserve">boolean</t>
+  </si>
+  <si>
     <t xml:space="preserve">WM/IsCompilation</t>
   </si>
   <si>
@@ -361,6 +376,9 @@
     <t xml:space="preserve">disk</t>
   </si>
   <si>
+    <t xml:space="preserve">tuple(int disc num, int total discs)</t>
+  </si>
+  <si>
     <t xml:space="preserve">WM/PartOfSet</t>
   </si>
   <si>
@@ -562,6 +580,9 @@
     <t xml:space="preserve">----:com.apple.iTunes:MEDIA</t>
   </si>
   <si>
+    <t xml:space="preserve">MP4FreeForm string</t>
+  </si>
+  <si>
     <t xml:space="preserve">WM/Media</t>
   </si>
   <si>
@@ -1002,6 +1023,12 @@
   </si>
   <si>
     <t xml:space="preserve">WM/Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St ring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">can be YYYY or YYYY-MM-DD</t>
   </si>
   <si>
     <t xml:space="preserve">Release Status</t>
@@ -1467,7 +1494,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1524,11 +1551,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1788,13 +1819,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD1048576"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="1" width="30.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="50.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="60.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="60.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="60.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.09"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1813,1615 +1847,1969 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>8</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>9</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
-        <v>14</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="4"/>
     </row>
     <row r="4" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="E5" s="9" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>28</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>29</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>33</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="4"/>
     </row>
     <row r="9" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>47</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>52</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>53</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>54</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>61</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>62</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>67</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>71</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>72</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>77</v>
+        <v>80</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="17" s="13" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>81</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="D17" s="12"/>
       <c r="E17" s="12" t="s">
-        <v>82</v>
+        <v>85</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="18" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>87</v>
+        <v>91</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>91</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="D19" s="4"/>
       <c r="E19" s="4" t="s">
-        <v>92</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>96</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
-        <v>97</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H20" s="4"/>
     </row>
     <row r="21" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>102</v>
+        <v>106</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>106</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="D22" s="4"/>
       <c r="E22" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="23" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>111</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" s="10" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>111</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="D23" s="9"/>
       <c r="E23" s="9" t="s">
-        <v>112</v>
+        <v>116</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>116</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="D24" s="4"/>
       <c r="E24" s="4" t="s">
-        <v>117</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>121</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="D25" s="4"/>
       <c r="E25" s="4" t="s">
-        <v>122</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="D26" s="4"/>
       <c r="E26" s="4" t="s">
-        <v>126</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="H26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>130</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="D27" s="4"/>
       <c r="E27" s="4" t="s">
-        <v>131</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="H27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>134</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D28" s="4"/>
       <c r="E28" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H28" s="4"/>
     </row>
     <row r="29" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>143</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
-        <v>144</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>148</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="D31" s="4"/>
       <c r="E31" s="4" t="s">
-        <v>149</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>153</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="D32" s="4"/>
       <c r="E32" s="4" t="s">
-        <v>154</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="H32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>158</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="D33" s="4"/>
       <c r="E33" s="4" t="s">
-        <v>159</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="H33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>163</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="D34" s="4"/>
       <c r="E34" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>167</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="D35" s="4"/>
       <c r="E35" s="4" t="s">
-        <v>168</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="H35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>172</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="D36" s="4"/>
       <c r="E36" s="4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="37" s="13" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>178</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" s="13" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>178</v>
+        <v>183</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>182</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="D38" s="4"/>
       <c r="E38" s="4" t="s">
-        <v>183</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="H38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>187</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="D39" s="4"/>
       <c r="E39" s="4" t="s">
-        <v>188</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="H39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>192</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="D40" s="4"/>
       <c r="E40" s="4" t="s">
-        <v>193</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>197</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="D41" s="4"/>
       <c r="E41" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>201</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="D42" s="4"/>
       <c r="E42" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>204</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="D43" s="4"/>
       <c r="E43" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>208</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="D44" s="4"/>
       <c r="E44" s="4" t="s">
-        <v>209</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="H44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>213</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="D45" s="4"/>
       <c r="E45" s="4" t="s">
-        <v>214</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="H45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>218</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="D46" s="4"/>
       <c r="E46" s="4" t="s">
-        <v>219</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="H46" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>223</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="D47" s="4"/>
       <c r="E47" s="4" t="s">
-        <v>224</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="H47" s="4"/>
     </row>
     <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>228</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="D48" s="4"/>
       <c r="E48" s="4" t="s">
-        <v>229</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="H48" s="4"/>
     </row>
     <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>233</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="D49" s="4"/>
       <c r="E49" s="4" t="s">
-        <v>234</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="H49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>238</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="D50" s="4"/>
       <c r="E50" s="4" t="s">
-        <v>239</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="H50" s="4"/>
     </row>
     <row r="51" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>243</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="D51" s="4"/>
       <c r="E51" s="4" t="s">
-        <v>244</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="H51" s="4"/>
     </row>
     <row r="52" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>248</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="D52" s="4"/>
       <c r="E52" s="4" t="s">
-        <v>249</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="H52" s="4"/>
     </row>
     <row r="53" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>253</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="D53" s="4"/>
       <c r="E53" s="4" t="s">
-        <v>254</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="H53" s="4"/>
     </row>
     <row r="54" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>258</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="D54" s="4"/>
       <c r="E54" s="4" t="s">
-        <v>259</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="H54" s="4"/>
     </row>
     <row r="55" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>263</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="D55" s="4"/>
       <c r="E55" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>267</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="D56" s="4"/>
       <c r="E56" s="4" t="s">
-        <v>268</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="H56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="D57" s="4"/>
       <c r="E57" s="4" t="s">
-        <v>272</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="H57" s="4"/>
     </row>
     <row r="58" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="D58" s="4"/>
       <c r="E58" s="4" t="s">
-        <v>276</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="H58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="D59" s="4"/>
       <c r="E59" s="4" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="60" s="14" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="C60" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="XFB60" s="13"/>
-      <c r="XFC60" s="13"/>
-      <c r="XFD60" s="13"/>
-    </row>
-    <row r="61" s="13" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>42</v>
+      </c>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="H59" s="4"/>
+    </row>
+    <row r="60" s="16" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="D60" s="15"/>
+      <c r="E60" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F60" s="15"/>
+      <c r="G60" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="H60" s="15"/>
+    </row>
+    <row r="61" s="13" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="11" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>288</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="D61" s="12"/>
       <c r="E61" s="12" t="s">
-        <v>289</v>
+        <v>295</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="H61" s="12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="D62" s="4"/>
       <c r="E62" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>295</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D63" s="4"/>
       <c r="E63" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>298</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D64" s="4"/>
       <c r="E64" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H64" s="4"/>
     </row>
     <row r="65" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>302</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="D65" s="4"/>
       <c r="E65" s="4" t="s">
-        <v>303</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="H65" s="4"/>
     </row>
     <row r="66" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="D66" s="4"/>
       <c r="E66" s="4" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="67" s="13" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>42</v>
+      </c>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="H66" s="4"/>
+    </row>
+    <row r="67" s="13" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="11" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>311</v>
+        <v>21</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>312</v>
+        <v>318</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="H67" s="12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>316</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="D68" s="4"/>
       <c r="E68" s="4" t="s">
-        <v>317</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="H68" s="4"/>
     </row>
     <row r="69" s="7" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>321</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="D69" s="6"/>
       <c r="E69" s="6" t="s">
-        <v>322</v>
+        <v>328</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>326</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="D70" s="4"/>
       <c r="E70" s="4" t="s">
-        <v>327</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="H70" s="4"/>
     </row>
     <row r="71" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>331</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="D71" s="4"/>
       <c r="E71" s="4" t="s">
-        <v>332</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="H71" s="4"/>
     </row>
     <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>336</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="D72" s="4"/>
       <c r="E72" s="4" t="s">
-        <v>337</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="H72" s="4"/>
     </row>
     <row r="73" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>341</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="D73" s="4"/>
       <c r="E73" s="4" t="s">
-        <v>342</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="H73" s="4"/>
     </row>
     <row r="74" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>346</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="D74" s="4"/>
       <c r="E74" s="4" t="s">
-        <v>347</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="H74" s="4"/>
     </row>
     <row r="75" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>351</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="D75" s="4"/>
       <c r="E75" s="4" t="s">
-        <v>352</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="H75" s="4"/>
     </row>
     <row r="76" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>356</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="D76" s="4"/>
       <c r="E76" s="4" t="s">
-        <v>357</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="H76" s="4"/>
     </row>
     <row r="77" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>361</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="D77" s="4"/>
       <c r="E77" s="4" t="s">
-        <v>362</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="H77" s="4"/>
     </row>
     <row r="78" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>366</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="D78" s="4"/>
       <c r="E78" s="4" t="s">
-        <v>367</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="H78" s="4"/>
     </row>
     <row r="79" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>371</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="D79" s="4"/>
       <c r="E79" s="4" t="s">
-        <v>372</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="H79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>376</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="D80" s="4"/>
       <c r="E80" s="4" t="s">
-        <v>377</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="H80" s="4"/>
     </row>
     <row r="81" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>380</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D81" s="4"/>
       <c r="E81" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H81" s="4"/>
     </row>
     <row r="82" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>383</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D82" s="4"/>
       <c r="E82" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H82" s="4"/>
     </row>
     <row r="83" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>387</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="D83" s="4"/>
       <c r="E83" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H83" s="4"/>
     </row>
     <row r="84" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>391</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="D84" s="4"/>
       <c r="E84" s="4" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="85" s="15" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>400</v>
+      </c>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="H84" s="4"/>
+    </row>
+    <row r="85" s="10" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>111</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="D85" s="9"/>
       <c r="E85" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="XFB85" s="10"/>
-      <c r="XFC85" s="10"/>
-      <c r="XFD85" s="10"/>
+        <v>116</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="H85" s="9"/>
     </row>
     <row r="86" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>399</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="D86" s="4"/>
       <c r="E86" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="87" s="15" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>408</v>
+      </c>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H86" s="4"/>
+    </row>
+    <row r="87" s="10" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="8" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>399</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="D87" s="9"/>
       <c r="E87" s="9" t="s">
-        <v>402</v>
-      </c>
-      <c r="XFB87" s="10"/>
-      <c r="XFC87" s="10"/>
-      <c r="XFD87" s="10"/>
+        <v>408</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="H87" s="9"/>
     </row>
     <row r="88" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>406</v>
+        <v>21</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>407</v>
+        <v>415</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>411</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="D89" s="4"/>
       <c r="E89" s="4" t="s">
-        <v>412</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="H89" s="4"/>
     </row>
     <row r="90" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="D90" s="4"/>
       <c r="E90" s="4" t="s">
-        <v>416</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="H90" s="4"/>
     </row>
     <row r="91" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>420</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="D91" s="4"/>
       <c r="E91" s="4" t="s">
-        <v>421</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="H91" s="4"/>
     </row>
     <row r="92" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="D92" s="4"/>
       <c r="E92" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H92" s="4"/>
     </row>
     <row r="94" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="16" t="s">
-        <v>425</v>
+      <c r="B94" s="17" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="1" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="1" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="1" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="1" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="1" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="1" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="1" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="1" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>443</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/src/generated_files/MusicBrainz_Picard_Tag_Map.xlsx
+++ b/src/generated_files/MusicBrainz_Picard_Tag_Map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\src\generated_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964A0833-8B8E-44AA-8274-0B85E5AA2E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA14D2F-7D74-4506-828C-9C4B7DC0939A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3835,6 +3835,9 @@
       <c r="B94" s="14"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H94">
+    <sortCondition ref="A2:A94"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/src/generated_files/MusicBrainz_Picard_Tag_Map.xlsx
+++ b/src/generated_files/MusicBrainz_Picard_Tag_Map.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\src\generated_files\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3B58A2-7161-4D00-85D4-E0B888B15937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,1368 +27,1365 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="447">
   <si>
-    <t xml:space="preserve">Tag Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internal Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID3v2 (mp3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID3v2 datatype</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iTunes MP4 (m4a)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MP4 datatype</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASF/Windows Media (wma)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASF datatype</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AcoustID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acoustid_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:Acoustid Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:Acoustid Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acoustid/Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.  Taken from the earliest release in the release group.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AcoustID Fingerprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acoustid_fingerprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:Acoustid Fingerprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:Acoustid Fingerprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acoustid/Fingerprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.  Used when uncertain whether composer or lyricist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Album</t>
-  </si>
-  <si>
-    <t xml:space="preserve">album</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TALB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">©alb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/AlbumTitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.  This is populated by LastFMPlus plugin and not by stock Picard.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Album Artist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">album_artist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPE2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aART</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/AlbumArtist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.  This is not able to be populated by stock Picard. It may be used and populated by certain plugins.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Album Artist Sort Order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">albumartistsort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSO2 (Picard&gt;=1.2)
+    <t>Tag Name</t>
+  </si>
+  <si>
+    <t>Internal Name</t>
+  </si>
+  <si>
+    <t>ID3v2 (mp3)</t>
+  </si>
+  <si>
+    <t>ID3v2 datatype</t>
+  </si>
+  <si>
+    <t>iTunes MP4 (m4a)</t>
+  </si>
+  <si>
+    <t>MP4 datatype</t>
+  </si>
+  <si>
+    <t>ASF/Windows Media (wma)</t>
+  </si>
+  <si>
+    <t>ASF datatype</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>AcoustID</t>
+  </si>
+  <si>
+    <t>acoustid_id</t>
+  </si>
+  <si>
+    <t>TXXX:Acoustid Id</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:Acoustid Id</t>
+  </si>
+  <si>
+    <t>Acoustid/Id</t>
+  </si>
+  <si>
+    <t>1.  Taken from the earliest release in the release group.</t>
+  </si>
+  <si>
+    <t>AcoustID Fingerprint</t>
+  </si>
+  <si>
+    <t>acoustid_fingerprint</t>
+  </si>
+  <si>
+    <t>TXXX:Acoustid Fingerprint</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:Acoustid Fingerprint</t>
+  </si>
+  <si>
+    <t>Acoustid/Fingerprint</t>
+  </si>
+  <si>
+    <t>2.  Used when uncertain whether composer or lyricist.</t>
+  </si>
+  <si>
+    <t>Album</t>
+  </si>
+  <si>
+    <t>album</t>
+  </si>
+  <si>
+    <t>TALB</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>©alb</t>
+  </si>
+  <si>
+    <t>WM/AlbumTitle</t>
+  </si>
+  <si>
+    <t>3.  This is populated by LastFMPlus plugin and not by stock Picard.</t>
+  </si>
+  <si>
+    <t>Album Artist</t>
+  </si>
+  <si>
+    <t>album_artist</t>
+  </si>
+  <si>
+    <t>TPE2</t>
+  </si>
+  <si>
+    <t>aART</t>
+  </si>
+  <si>
+    <t>WM/AlbumArtist</t>
+  </si>
+  <si>
+    <t>4.  This is not able to be populated by stock Picard. It may be used and populated by certain plugins.</t>
+  </si>
+  <si>
+    <t>Album Artist Sort Order</t>
+  </si>
+  <si>
+    <t>albumartistsort</t>
+  </si>
+  <si>
+    <t>TSO2 (Picard&gt;=1.2)
 TXXX:ALBUMARTISTSORT (Picard&lt;=1.1)</t>
   </si>
   <si>
-    <t xml:space="preserve">soaa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/AlbumArtistSortOrder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.  For Picard&gt;=1.3 this indicates a Various Artists album; for Picard&lt;=1.2 this indicates albums with tracks by different artists which is incorrect (e.g.: an original album with a duet with a feat. artist would show as a Compilation). In neither case does this indicate a MusicBrainz Release Group subtype of compilation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Album Sort Order [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">albumsort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSOA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/AlbumSortOrder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.  Release-level license relationship type.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arranger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arranger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIPL:arranger (ID3v2.4)
+    <t>soaa</t>
+  </si>
+  <si>
+    <t>WM/AlbumArtistSortOrder</t>
+  </si>
+  <si>
+    <t>5.  For Picard&gt;=1.3 this indicates a Various Artists album; for Picard&lt;=1.2 this indicates albums with tracks by different artists which is incorrect (e.g.: an original album with a duet with a feat. artist would show as a Compilation). In neither case does this indicate a MusicBrainz Release Group subtype of compilation.</t>
+  </si>
+  <si>
+    <t>Album Sort Order [4]</t>
+  </si>
+  <si>
+    <t>albumsort</t>
+  </si>
+  <si>
+    <t>TSOA</t>
+  </si>
+  <si>
+    <t>soal</t>
+  </si>
+  <si>
+    <t>WM/AlbumSortOrder</t>
+  </si>
+  <si>
+    <t>6.  Release-level license relationship type.</t>
+  </si>
+  <si>
+    <t>Arranger</t>
+  </si>
+  <si>
+    <t>arranger</t>
+  </si>
+  <si>
+    <t>TIPL:arranger (ID3v2.4)
 IPLS:arranger (ID3v2.3)</t>
   </si>
   <si>
-    <t xml:space="preserve">n/a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.  Recording-level license relationship type.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">artist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">©ART</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.  With "Save iTunes compatible grouping and work" (since Picard&gt;=2.1.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artist Sort Order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">artistsort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSOP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/ArtistSortOrder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.  From iTunes Metadata Format Specification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">artists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:ARTISTS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:ARTISTS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/ARTISTS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">asin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:ASIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:ASIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barcode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">barcode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:BARCODE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:BARCODE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/Barcode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPM [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bpm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBPM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tmpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/BeatsPerMinute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalog Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">catalognumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:CATALOGNUMBER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:CATALOGNUMBER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/CatalogNo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comment [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMM::lng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">©cmt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compilation (iTunes) [5]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">compilation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/IsCompilation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Composer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">composer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">©wrt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/Composer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Composer Sort Order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">composersort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSOC (Picard&gt;=1.3)
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>7.  Recording-level license relationship type.</t>
+  </si>
+  <si>
+    <t>Artist</t>
+  </si>
+  <si>
+    <t>artist</t>
+  </si>
+  <si>
+    <t>TPE1</t>
+  </si>
+  <si>
+    <t>©ART</t>
+  </si>
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>8.  With "Save iTunes compatible grouping and work" (since Picard&gt;=2.1.0)</t>
+  </si>
+  <si>
+    <t>Artist Sort Order</t>
+  </si>
+  <si>
+    <t>artistsort</t>
+  </si>
+  <si>
+    <t>TSOP</t>
+  </si>
+  <si>
+    <t>soar</t>
+  </si>
+  <si>
+    <t>WM/ArtistSortOrder</t>
+  </si>
+  <si>
+    <t>9.  From iTunes Metadata Format Specification</t>
+  </si>
+  <si>
+    <t>Artists</t>
+  </si>
+  <si>
+    <t>artists</t>
+  </si>
+  <si>
+    <t>TXXX:ARTISTS</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:ARTISTS</t>
+  </si>
+  <si>
+    <t>WM/ARTISTS</t>
+  </si>
+  <si>
+    <t>ASIN</t>
+  </si>
+  <si>
+    <t>asin</t>
+  </si>
+  <si>
+    <t>TXXX:ASIN</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:ASIN</t>
+  </si>
+  <si>
+    <t>Barcode</t>
+  </si>
+  <si>
+    <t>barcode</t>
+  </si>
+  <si>
+    <t>TXXX:BARCODE</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:BARCODE</t>
+  </si>
+  <si>
+    <t>WM/Barcode</t>
+  </si>
+  <si>
+    <t>BPM [4]</t>
+  </si>
+  <si>
+    <t>bpm</t>
+  </si>
+  <si>
+    <t>TBPM</t>
+  </si>
+  <si>
+    <t>tmpo</t>
+  </si>
+  <si>
+    <t>WM/BeatsPerMinute</t>
+  </si>
+  <si>
+    <t>Catalog Number</t>
+  </si>
+  <si>
+    <t>catalognumber</t>
+  </si>
+  <si>
+    <t>TXXX:CATALOGNUMBER</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:CATALOGNUMBER</t>
+  </si>
+  <si>
+    <t>WM/CatalogNo</t>
+  </si>
+  <si>
+    <t>Comment [4]</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>COMM::lng</t>
+  </si>
+  <si>
+    <t>©cmt</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Compilation (iTunes) [5]</t>
+  </si>
+  <si>
+    <t>compilation</t>
+  </si>
+  <si>
+    <t>TCMP</t>
+  </si>
+  <si>
+    <t>cpil</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>WM/IsCompilation</t>
+  </si>
+  <si>
+    <t>Composer</t>
+  </si>
+  <si>
+    <t>composer</t>
+  </si>
+  <si>
+    <t>TCOM</t>
+  </si>
+  <si>
+    <t>©wrt</t>
+  </si>
+  <si>
+    <t>WM/Composer</t>
+  </si>
+  <si>
+    <t>Composer Sort Order</t>
+  </si>
+  <si>
+    <t>composersort</t>
+  </si>
+  <si>
+    <t>TSOC (Picard&gt;=1.3)
 TXXX:COMPOSERSORT (Picard&lt;=1.2)</t>
   </si>
   <si>
-    <t xml:space="preserve">soco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/ComposerSortOrder (Picard&gt;=1.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conductor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">conductor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPE3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:CONDUCTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/Conductor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copyright [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">copyright</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCOP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cprt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copyright</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director</t>
-  </si>
-  <si>
-    <t xml:space="preserve">director</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:DIRECTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">©dir [9]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/Director</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disc Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">disc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">disk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tuple(int disc num, int total discs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/PartOfSet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disc Subtitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">discsubtitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSST (ID3v2.4 only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:DISCSUBTITLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/SetSubTitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Encoded By [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">encodedby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TENC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">©too</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/EncodedBy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Encoder Settings [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">encodersettings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/EncodingSettings (Picard&gt;=1.3.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIPL:engineer (ID3v2.4)
+    <t>soco</t>
+  </si>
+  <si>
+    <t>WM/ComposerSortOrder (Picard&gt;=1.3)</t>
+  </si>
+  <si>
+    <t>Conductor</t>
+  </si>
+  <si>
+    <t>conductor</t>
+  </si>
+  <si>
+    <t>TPE3</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:CONDUCTOR</t>
+  </si>
+  <si>
+    <t>WM/Conductor</t>
+  </si>
+  <si>
+    <t>Copyright [4]</t>
+  </si>
+  <si>
+    <t>copyright</t>
+  </si>
+  <si>
+    <t>TCOP</t>
+  </si>
+  <si>
+    <t>cprt</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>director</t>
+  </si>
+  <si>
+    <t>TXXX:DIRECTOR</t>
+  </si>
+  <si>
+    <t>©dir [9]</t>
+  </si>
+  <si>
+    <t>WM/Director</t>
+  </si>
+  <si>
+    <t>Disc Number</t>
+  </si>
+  <si>
+    <t>disc</t>
+  </si>
+  <si>
+    <t>TPOS</t>
+  </si>
+  <si>
+    <t>disk</t>
+  </si>
+  <si>
+    <t>tuple(int disc num, int total discs)</t>
+  </si>
+  <si>
+    <t>WM/PartOfSet</t>
+  </si>
+  <si>
+    <t>Disc Subtitle</t>
+  </si>
+  <si>
+    <t>discsubtitle</t>
+  </si>
+  <si>
+    <t>TSST (ID3v2.4 only)</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:DISCSUBTITLE</t>
+  </si>
+  <si>
+    <t>WM/SetSubTitle</t>
+  </si>
+  <si>
+    <t>Encoded By [4]</t>
+  </si>
+  <si>
+    <t>encodedby</t>
+  </si>
+  <si>
+    <t>TENC</t>
+  </si>
+  <si>
+    <t>©too</t>
+  </si>
+  <si>
+    <t>WM/EncodedBy</t>
+  </si>
+  <si>
+    <t>Encoder Settings [4]</t>
+  </si>
+  <si>
+    <t>encodersettings</t>
+  </si>
+  <si>
+    <t>TSSE</t>
+  </si>
+  <si>
+    <t>WM/EncodingSettings (Picard&gt;=1.3.1)</t>
+  </si>
+  <si>
+    <t>Engineer</t>
+  </si>
+  <si>
+    <t>engineer</t>
+  </si>
+  <si>
+    <t>TIPL:engineer (ID3v2.4)
 IPLS:engineer (ID3v2.3)</t>
   </si>
   <si>
-    <t xml:space="preserve">----:com.apple.iTunes:ENGINEER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gapless Playback [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gapless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pgap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">genre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">©gen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/Genre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grouping [3]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grouping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIT1
+    <t>----:com.apple.iTunes:ENGINEER</t>
+  </si>
+  <si>
+    <t>WM/Engineer</t>
+  </si>
+  <si>
+    <t>Gapless Playback [4]</t>
+  </si>
+  <si>
+    <t>gapless</t>
+  </si>
+  <si>
+    <t>pgap</t>
+  </si>
+  <si>
+    <t>Genre</t>
+  </si>
+  <si>
+    <t>genre</t>
+  </si>
+  <si>
+    <t>TCON</t>
+  </si>
+  <si>
+    <t>©gen</t>
+  </si>
+  <si>
+    <t>WM/Genre</t>
+  </si>
+  <si>
+    <t>Grouping [3]</t>
+  </si>
+  <si>
+    <t>grouping</t>
+  </si>
+  <si>
+    <t>TIT1
 GRP1 [8]</t>
   </si>
   <si>
-    <t xml:space="preserve">©grp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/ContentGroupDescription</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Initial Key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key (Picard&gt;=1.4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TKEY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:initialkey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/InitialKey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">isrc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:ISRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/ISRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:LANGUAGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/Language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">License [6] [7]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">license</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WCOP (single URL)
+    <t>©grp</t>
+  </si>
+  <si>
+    <t>WM/ContentGroupDescription</t>
+  </si>
+  <si>
+    <t>Initial Key</t>
+  </si>
+  <si>
+    <t>key (Picard&gt;=1.4)</t>
+  </si>
+  <si>
+    <t>TKEY</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:initialkey</t>
+  </si>
+  <si>
+    <t>WM/InitialKey</t>
+  </si>
+  <si>
+    <t>ISRC</t>
+  </si>
+  <si>
+    <t>isrc</t>
+  </si>
+  <si>
+    <t>TSRC</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:ISRC</t>
+  </si>
+  <si>
+    <t>WM/ISRC</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>language</t>
+  </si>
+  <si>
+    <t>TLAN</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:LANGUAGE</t>
+  </si>
+  <si>
+    <t>WM/Language</t>
+  </si>
+  <si>
+    <t>License [6] [7]</t>
+  </si>
+  <si>
+    <t>license</t>
+  </si>
+  <si>
+    <t>WCOP (single URL)
 TXXX:LICENSE (multiple or non-URL)</t>
   </si>
   <si>
-    <t xml:space="preserve">----:com.apple.iTunes:LICENSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lyricist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lyricist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEXT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:LYRICIST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/Writer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lyrics [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lyrics:description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USLT:description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">©lyr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/Lyrics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media</t>
-  </si>
-  <si>
-    <t xml:space="preserve">media</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MEDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MP4FreeForm string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/Media</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mix-DJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">djmixer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIPL:DJ-mix (ID3v2.4)
+    <t>----:com.apple.iTunes:LICENSE</t>
+  </si>
+  <si>
+    <t>Lyricist</t>
+  </si>
+  <si>
+    <t>lyricist</t>
+  </si>
+  <si>
+    <t>TEXT</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:LYRICIST</t>
+  </si>
+  <si>
+    <t>WM/Writer</t>
+  </si>
+  <si>
+    <t>Lyrics [4]</t>
+  </si>
+  <si>
+    <t>lyrics:description</t>
+  </si>
+  <si>
+    <t>USLT:description</t>
+  </si>
+  <si>
+    <t>©lyr</t>
+  </si>
+  <si>
+    <t>WM/Lyrics</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>media</t>
+  </si>
+  <si>
+    <t>TMED</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MEDIA</t>
+  </si>
+  <si>
+    <t>MP4FreeForm string</t>
+  </si>
+  <si>
+    <t>WM/Media</t>
+  </si>
+  <si>
+    <t>Mix-DJ</t>
+  </si>
+  <si>
+    <t>djmixer</t>
+  </si>
+  <si>
+    <t>TIPL:DJ-mix (ID3v2.4)
 IPLS:DJ-mix (ID3v2.3)</t>
   </si>
   <si>
-    <t xml:space="preserve">----:com.apple.iTunes:DJMIXER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/DJMixer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mixer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mixer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIPL:mix (ID3v2.4)
+    <t>----:com.apple.iTunes:DJMIXER</t>
+  </si>
+  <si>
+    <t>WM/DJMixer</t>
+  </si>
+  <si>
+    <t>Mixer</t>
+  </si>
+  <si>
+    <t>mixer</t>
+  </si>
+  <si>
+    <t>TIPL:mix (ID3v2.4)
 IPLS:mix (ID3v2.3)</t>
   </si>
   <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MIXER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/Mixer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mood [3]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMOO (ID3v2.4 only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MOOD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/Mood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movement [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">movement (Picard&gt;=2.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MVNM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">©mvn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movement Count [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">movementtotal (Picard&gt;=2.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MVIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mvc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movement Number [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">movementnumber (Picard&gt;=2.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mvi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz Artist ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">musicbrainz_artistid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:MusicBrainz Artist Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MusicBrainz Artist Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz/Artist Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz Disc ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">musicbrainz_discid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:MusicBrainz Disc Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MusicBrainz Disc Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz/Disc Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz Original Artist ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">musicbrainz_originalartistid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:MusicBrainz Original Artist Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MusicBrainz Original Artist Id (Picard&gt;=2.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz/Original Artist Id (Picard&gt;=2.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz Original Release ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">musicbrainz_originalalbumid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:MusicBrainz Original Album Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MusicBrainz Original Album Id (Picard&gt;=2.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz/Original Album Id (Picard&gt;=2.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz Recording ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">musicbrainz_recordingid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UFID:http://musicbrainz.org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MusicBrainz Track Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz/Track Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz Release Artist ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">musicbrainz_albumartistid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:MusicBrainz Album Artist Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MusicBrainz Album Artist Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz/Album Artist Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz Release Group ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">musicbrainz_releasegroupid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:MusicBrainz Release Group Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MusicBrainz Release Group Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz/Release Group Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz Release ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">musicbrainz_albumid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:MusicBrainz Album Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MusicBrainz Album Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz/Album Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz Track ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">musicbrainz_trackid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:MusicBrainz Release Track Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MusicBrainz Release Track Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz/Release Track Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz TRM ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">musicbrainz_trmid (deprecated)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:MusicBrainz TRM Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MusicBrainz TRM Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz/TRM Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz Work ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">musicbrainz_workid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:MusicBrainz Work Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MusicBrainz Work Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz/Work Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicIP Fingerprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">musicip_fingerprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:MusicMagic Fingerprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:fingerprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicIP PUID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">musicip_puid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:MusicIP PUID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MusicIP PUID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicIP/PUID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Original Album</t>
-  </si>
-  <si>
-    <t xml:space="preserve">originalalbum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/OriginalAlbumTitle (Picard&gt;=2.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Original Artist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">originalartist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/OriginalArtist (Picard&gt;=2.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Original Filename</t>
-  </si>
-  <si>
-    <t xml:space="preserve">originalfilename (Picard&gt;=2.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOFN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/OriginalFilename</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Original Release Date [1]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">originaldate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TDOR (ID3v2.4)
+    <t>----:com.apple.iTunes:MIXER</t>
+  </si>
+  <si>
+    <t>WM/Mixer</t>
+  </si>
+  <si>
+    <t>Mood [3]</t>
+  </si>
+  <si>
+    <t>mood</t>
+  </si>
+  <si>
+    <t>TMOO (ID3v2.4 only)</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MOOD</t>
+  </si>
+  <si>
+    <t>WM/Mood</t>
+  </si>
+  <si>
+    <t>Movement [4]</t>
+  </si>
+  <si>
+    <t>movement (Picard&gt;=2.1)</t>
+  </si>
+  <si>
+    <t>MVNM</t>
+  </si>
+  <si>
+    <t>©mvn</t>
+  </si>
+  <si>
+    <t>Movement Count [4]</t>
+  </si>
+  <si>
+    <t>movementtotal (Picard&gt;=2.1)</t>
+  </si>
+  <si>
+    <t>MVIN</t>
+  </si>
+  <si>
+    <t>mvc</t>
+  </si>
+  <si>
+    <t>Movement Number [4]</t>
+  </si>
+  <si>
+    <t>movementnumber (Picard&gt;=2.1)</t>
+  </si>
+  <si>
+    <t>mvi</t>
+  </si>
+  <si>
+    <t>MusicBrainz Artist ID</t>
+  </si>
+  <si>
+    <t>musicbrainz_artistid</t>
+  </si>
+  <si>
+    <t>TXXX:MusicBrainz Artist Id</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MusicBrainz Artist Id</t>
+  </si>
+  <si>
+    <t>MusicBrainz/Artist Id</t>
+  </si>
+  <si>
+    <t>MusicBrainz Disc ID</t>
+  </si>
+  <si>
+    <t>musicbrainz_discid</t>
+  </si>
+  <si>
+    <t>TXXX:MusicBrainz Disc Id</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MusicBrainz Disc Id</t>
+  </si>
+  <si>
+    <t>MusicBrainz/Disc Id</t>
+  </si>
+  <si>
+    <t>MusicBrainz Original Artist ID</t>
+  </si>
+  <si>
+    <t>musicbrainz_originalartistid</t>
+  </si>
+  <si>
+    <t>TXXX:MusicBrainz Original Artist Id</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MusicBrainz Original Artist Id (Picard&gt;=2.1)</t>
+  </si>
+  <si>
+    <t>MusicBrainz/Original Artist Id (Picard&gt;=2.1)</t>
+  </si>
+  <si>
+    <t>MusicBrainz Original Release ID</t>
+  </si>
+  <si>
+    <t>musicbrainz_originalalbumid</t>
+  </si>
+  <si>
+    <t>TXXX:MusicBrainz Original Album Id</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MusicBrainz Original Album Id (Picard&gt;=2.1)</t>
+  </si>
+  <si>
+    <t>MusicBrainz/Original Album Id (Picard&gt;=2.1)</t>
+  </si>
+  <si>
+    <t>MusicBrainz Recording ID</t>
+  </si>
+  <si>
+    <t>musicbrainz_recordingid</t>
+  </si>
+  <si>
+    <t>UFID:http://musicbrainz.org</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MusicBrainz Track Id</t>
+  </si>
+  <si>
+    <t>MusicBrainz/Track Id</t>
+  </si>
+  <si>
+    <t>MusicBrainz Release Artist ID</t>
+  </si>
+  <si>
+    <t>musicbrainz_albumartistid</t>
+  </si>
+  <si>
+    <t>TXXX:MusicBrainz Album Artist Id</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MusicBrainz Album Artist Id</t>
+  </si>
+  <si>
+    <t>MusicBrainz/Album Artist Id</t>
+  </si>
+  <si>
+    <t>MusicBrainz Release Group ID</t>
+  </si>
+  <si>
+    <t>musicbrainz_releasegroupid</t>
+  </si>
+  <si>
+    <t>TXXX:MusicBrainz Release Group Id</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MusicBrainz Release Group Id</t>
+  </si>
+  <si>
+    <t>MusicBrainz/Release Group Id</t>
+  </si>
+  <si>
+    <t>MusicBrainz Release ID</t>
+  </si>
+  <si>
+    <t>musicbrainz_albumid</t>
+  </si>
+  <si>
+    <t>TXXX:MusicBrainz Album Id</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MusicBrainz Album Id</t>
+  </si>
+  <si>
+    <t>MusicBrainz/Album Id</t>
+  </si>
+  <si>
+    <t>MusicBrainz Track ID</t>
+  </si>
+  <si>
+    <t>musicbrainz_trackid</t>
+  </si>
+  <si>
+    <t>TXXX:MusicBrainz Release Track Id</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MusicBrainz Release Track Id</t>
+  </si>
+  <si>
+    <t>MusicBrainz/Release Track Id</t>
+  </si>
+  <si>
+    <t>MusicBrainz TRM ID</t>
+  </si>
+  <si>
+    <t>musicbrainz_trmid (deprecated)</t>
+  </si>
+  <si>
+    <t>TXXX:MusicBrainz TRM Id</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MusicBrainz TRM Id</t>
+  </si>
+  <si>
+    <t>MusicBrainz/TRM Id</t>
+  </si>
+  <si>
+    <t>MusicBrainz Work ID</t>
+  </si>
+  <si>
+    <t>musicbrainz_workid</t>
+  </si>
+  <si>
+    <t>TXXX:MusicBrainz Work Id</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MusicBrainz Work Id</t>
+  </si>
+  <si>
+    <t>MusicBrainz/Work Id</t>
+  </si>
+  <si>
+    <t>MusicIP Fingerprint</t>
+  </si>
+  <si>
+    <t>musicip_fingerprint</t>
+  </si>
+  <si>
+    <t>TXXX:MusicMagic Fingerprint</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:fingerprint</t>
+  </si>
+  <si>
+    <t>MusicIP PUID</t>
+  </si>
+  <si>
+    <t>musicip_puid</t>
+  </si>
+  <si>
+    <t>TXXX:MusicIP PUID</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MusicIP PUID</t>
+  </si>
+  <si>
+    <t>MusicIP/PUID</t>
+  </si>
+  <si>
+    <t>Original Album</t>
+  </si>
+  <si>
+    <t>originalalbum</t>
+  </si>
+  <si>
+    <t>TOAL</t>
+  </si>
+  <si>
+    <t>WM/OriginalAlbumTitle (Picard&gt;=2.1)</t>
+  </si>
+  <si>
+    <t>Original Artist</t>
+  </si>
+  <si>
+    <t>originalartist</t>
+  </si>
+  <si>
+    <t>TOPE</t>
+  </si>
+  <si>
+    <t>WM/OriginalArtist (Picard&gt;=2.1)</t>
+  </si>
+  <si>
+    <t>Original Filename</t>
+  </si>
+  <si>
+    <t>originalfilename (Picard&gt;=2.3)</t>
+  </si>
+  <si>
+    <t>TOFN</t>
+  </si>
+  <si>
+    <t>WM/OriginalFilename</t>
+  </si>
+  <si>
+    <t>Original Release Date [1]</t>
+  </si>
+  <si>
+    <t>originaldate</t>
+  </si>
+  <si>
+    <t>TDOR (ID3v2.4)
 TORY (ID3v2.3)</t>
   </si>
   <si>
-    <t xml:space="preserve">WM/OriginalReleaseTime (Picard&gt;=1.3.1)
+    <t>WM/OriginalReleaseTime (Picard&gt;=1.3.1)
 WM/OriginalReleaseYear (Picard&lt;=1.3.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">Original Release Year [1]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">originalyear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:originalyear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/OriginalReleaseYear (Picard&gt;=1.3.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">performer:instrument</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMCL:instrument (ID3v2.4)
+    <t>Original Release Year [1]</t>
+  </si>
+  <si>
+    <t>originalyear</t>
+  </si>
+  <si>
+    <t>TORY</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:originalyear</t>
+  </si>
+  <si>
+    <t>WM/OriginalReleaseYear (Picard&gt;=1.3.1)</t>
+  </si>
+  <si>
+    <t>Performer</t>
+  </si>
+  <si>
+    <t>performer:instrument</t>
+  </si>
+  <si>
+    <t>TMCL:instrument (ID3v2.4)
 IPLS:instrument (ID3v2.3)</t>
   </si>
   <si>
-    <t xml:space="preserve">Podcast [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">podcast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pcst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Podcast URL [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">podcasturl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">purl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Producer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">producer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIPL:producer (ID3v2.4)
+    <t>Podcast [4]</t>
+  </si>
+  <si>
+    <t>podcast</t>
+  </si>
+  <si>
+    <t>pcst</t>
+  </si>
+  <si>
+    <t>Podcast URL [4]</t>
+  </si>
+  <si>
+    <t>podcasturl</t>
+  </si>
+  <si>
+    <t>purl</t>
+  </si>
+  <si>
+    <t>Producer</t>
+  </si>
+  <si>
+    <t>producer</t>
+  </si>
+  <si>
+    <t>TIPL:producer (ID3v2.4)
 IPLS:producer (ID3v2.3)</t>
   </si>
   <si>
-    <t xml:space="preserve">----:com.apple.iTunes:PRODUCER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/Producer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POPM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/SharedUserRating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Record Label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">publisher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPUB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:LABEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/Publisher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release Country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">releasecountry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:MusicBrainz Album Release Country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MusicBrainz Album Release Country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz/Album Release Country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TDRC (ID3v2.4)
+    <t>----:com.apple.iTunes:PRODUCER</t>
+  </si>
+  <si>
+    <t>WM/Producer</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>_rating</t>
+  </si>
+  <si>
+    <t>POPM</t>
+  </si>
+  <si>
+    <t>WM/SharedUserRating</t>
+  </si>
+  <si>
+    <t>Record Label</t>
+  </si>
+  <si>
+    <t>publisher</t>
+  </si>
+  <si>
+    <t>TPUB</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:LABEL</t>
+  </si>
+  <si>
+    <t>WM/Publisher</t>
+  </si>
+  <si>
+    <t>Release Country</t>
+  </si>
+  <si>
+    <t>releasecountry</t>
+  </si>
+  <si>
+    <t>TXXX:MusicBrainz Album Release Country</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MusicBrainz Album Release Country</t>
+  </si>
+  <si>
+    <t>MusicBrainz/Album Release Country</t>
+  </si>
+  <si>
+    <t>Release Date</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>TDRC (ID3v2.4)
 TYER + TDAT (ID3v2.3)</t>
   </si>
   <si>
-    <t xml:space="preserve">©day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/Year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">St ring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">can be YYYY or YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">releasestatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:MusicBrainz Album Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MusicBrainz Album Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz/Album Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">releasetype</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:MusicBrainz Album Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:MusicBrainz Album Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MusicBrainz/Album Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remixer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remixer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPE4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:REMIXER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/ModifiedBy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReplayGain Album Gain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replaygain_album_gain (Picard&gt;=2.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:REPLAYGAIN_ALBUM_GAIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:REPLAYGAIN_ALBUM_GAIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REPLAYGAIN_ALBUM_GAIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReplayGain Album Peak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replaygain_album_peak (Picard&gt;=2.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:REPLAYGAIN_ALBUM_PEAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:REPLAYGAIN_ALBUM_PEAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REPLAYGAIN_ALBUM_PEAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReplayGain Album Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replaygain_album_range (Picard&gt;=2.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:REPLAYGAIN_ALBUM_RANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:REPLAYGAIN_ALBUM_RANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REPLAYGAIN_ALBUM_RANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReplayGain Reference Loudness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replaygain_reference_loudness (Picard&gt;=2.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:REPLAYGAIN_REFERENCE_LOUDNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:REPLAYGAIN_REFERENCE_LOUDNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REPLAYGAIN_REFERENCE_LOUDNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReplayGain Track Gain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replaygain_track_gain (Picard&gt;=2.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:REPLAYGAIN_TRACK_GAIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:REPLAYGAIN_TRACK_GAIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REPLAYGAIN_TRACK_GAIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReplayGain Track Peak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replaygain_track_peak (Picard&gt;=2.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:REPLAYGAIN_TRACK_PEAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:REPLAYGAIN_TRACK_PEAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REPLAYGAIN_TRACK_PEAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReplayGain Track Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replaygain_track_range (Picard&gt;=2.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:REPLAYGAIN_TRACK_RANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:REPLAYGAIN_TRACK_RANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REPLAYGAIN_TRACK_RANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Script</t>
-  </si>
-  <si>
-    <t xml:space="preserve">script</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:SCRIPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:SCRIPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/Script</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Show Name [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">show</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tvsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Show Name Sort Order [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">showsort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sosn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Show Work &amp; Movement [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">showmovement (Picard&gt;=2.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:SHOWMOVEMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shwm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subtitle [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subtitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----:com.apple.iTunes:SUBTITLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/SubTitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Discs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">totaldiscs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">disc num/total discs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/PartOfSet (Picard&gt;=1.3.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string (n/n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Tracks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">totaltracks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trkn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Track Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tracknumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">track num/total tracks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/TrackNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Track Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">©nam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Track Title Sort Order [4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">titlesort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSOT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sonm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/TitleSortOrder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website (official artist website)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WOAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/AuthorURL (Picard&gt;=1.3.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Work Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">work (Picard&gt;=1.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:WORK TIT1 [8]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">©wrk (Picard&gt;=2.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WM/Work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Writer [2]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">writer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXXX:Writer (Picard&gt;=1.3)</t>
+    <t>©day</t>
+  </si>
+  <si>
+    <t>WM/Year</t>
+  </si>
+  <si>
+    <t>St ring</t>
+  </si>
+  <si>
+    <t>can be YYYY or YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>Release Status</t>
+  </si>
+  <si>
+    <t>releasestatus</t>
+  </si>
+  <si>
+    <t>TXXX:MusicBrainz Album Status</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MusicBrainz Album Status</t>
+  </si>
+  <si>
+    <t>MusicBrainz/Album Status</t>
+  </si>
+  <si>
+    <t>Release Type</t>
+  </si>
+  <si>
+    <t>releasetype</t>
+  </si>
+  <si>
+    <t>TXXX:MusicBrainz Album Type</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MusicBrainz Album Type</t>
+  </si>
+  <si>
+    <t>MusicBrainz/Album Type</t>
+  </si>
+  <si>
+    <t>Remixer</t>
+  </si>
+  <si>
+    <t>remixer</t>
+  </si>
+  <si>
+    <t>TPE4</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:REMIXER</t>
+  </si>
+  <si>
+    <t>WM/ModifiedBy</t>
+  </si>
+  <si>
+    <t>ReplayGain Album Gain</t>
+  </si>
+  <si>
+    <t>replaygain_album_gain (Picard&gt;=2.2)</t>
+  </si>
+  <si>
+    <t>TXXX:REPLAYGAIN_ALBUM_GAIN</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:REPLAYGAIN_ALBUM_GAIN</t>
+  </si>
+  <si>
+    <t>REPLAYGAIN_ALBUM_GAIN</t>
+  </si>
+  <si>
+    <t>ReplayGain Album Peak</t>
+  </si>
+  <si>
+    <t>replaygain_album_peak (Picard&gt;=2.2)</t>
+  </si>
+  <si>
+    <t>TXXX:REPLAYGAIN_ALBUM_PEAK</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:REPLAYGAIN_ALBUM_PEAK</t>
+  </si>
+  <si>
+    <t>REPLAYGAIN_ALBUM_PEAK</t>
+  </si>
+  <si>
+    <t>ReplayGain Album Range</t>
+  </si>
+  <si>
+    <t>replaygain_album_range (Picard&gt;=2.2)</t>
+  </si>
+  <si>
+    <t>TXXX:REPLAYGAIN_ALBUM_RANGE</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:REPLAYGAIN_ALBUM_RANGE</t>
+  </si>
+  <si>
+    <t>REPLAYGAIN_ALBUM_RANGE</t>
+  </si>
+  <si>
+    <t>ReplayGain Reference Loudness</t>
+  </si>
+  <si>
+    <t>replaygain_reference_loudness (Picard&gt;=2.2)</t>
+  </si>
+  <si>
+    <t>TXXX:REPLAYGAIN_REFERENCE_LOUDNESS</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:REPLAYGAIN_REFERENCE_LOUDNESS</t>
+  </si>
+  <si>
+    <t>REPLAYGAIN_REFERENCE_LOUDNESS</t>
+  </si>
+  <si>
+    <t>ReplayGain Track Gain</t>
+  </si>
+  <si>
+    <t>replaygain_track_gain (Picard&gt;=2.2)</t>
+  </si>
+  <si>
+    <t>TXXX:REPLAYGAIN_TRACK_GAIN</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:REPLAYGAIN_TRACK_GAIN</t>
+  </si>
+  <si>
+    <t>REPLAYGAIN_TRACK_GAIN</t>
+  </si>
+  <si>
+    <t>ReplayGain Track Peak</t>
+  </si>
+  <si>
+    <t>replaygain_track_peak (Picard&gt;=2.2)</t>
+  </si>
+  <si>
+    <t>TXXX:REPLAYGAIN_TRACK_PEAK</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:REPLAYGAIN_TRACK_PEAK</t>
+  </si>
+  <si>
+    <t>REPLAYGAIN_TRACK_PEAK</t>
+  </si>
+  <si>
+    <t>ReplayGain Track Range</t>
+  </si>
+  <si>
+    <t>replaygain_track_range (Picard&gt;=2.2)</t>
+  </si>
+  <si>
+    <t>TXXX:REPLAYGAIN_TRACK_RANGE</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:REPLAYGAIN_TRACK_RANGE</t>
+  </si>
+  <si>
+    <t>REPLAYGAIN_TRACK_RANGE</t>
+  </si>
+  <si>
+    <t>Script</t>
+  </si>
+  <si>
+    <t>script</t>
+  </si>
+  <si>
+    <t>TXXX:SCRIPT</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:SCRIPT</t>
+  </si>
+  <si>
+    <t>WM/Script</t>
+  </si>
+  <si>
+    <t>Show Name [4]</t>
+  </si>
+  <si>
+    <t>show</t>
+  </si>
+  <si>
+    <t>tvsh</t>
+  </si>
+  <si>
+    <t>Show Name Sort Order [4]</t>
+  </si>
+  <si>
+    <t>showsort</t>
+  </si>
+  <si>
+    <t>sosn</t>
+  </si>
+  <si>
+    <t>Show Work &amp; Movement [4]</t>
+  </si>
+  <si>
+    <t>showmovement (Picard&gt;=2.1)</t>
+  </si>
+  <si>
+    <t>TXXX:SHOWMOVEMENT</t>
+  </si>
+  <si>
+    <t>shwm</t>
+  </si>
+  <si>
+    <t>Subtitle [4]</t>
+  </si>
+  <si>
+    <t>subtitle</t>
+  </si>
+  <si>
+    <t>TIT3</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:SUBTITLE</t>
+  </si>
+  <si>
+    <t>WM/SubTitle</t>
+  </si>
+  <si>
+    <t>Total Discs</t>
+  </si>
+  <si>
+    <t>totaldiscs</t>
+  </si>
+  <si>
+    <t>disc num/total discs</t>
+  </si>
+  <si>
+    <t>WM/PartOfSet (Picard&gt;=1.3.1)</t>
+  </si>
+  <si>
+    <t>string (n/n)</t>
+  </si>
+  <si>
+    <t>Total Tracks</t>
+  </si>
+  <si>
+    <t>totaltracks</t>
+  </si>
+  <si>
+    <t>TRCK</t>
+  </si>
+  <si>
+    <t>trkn</t>
+  </si>
+  <si>
+    <t>Track Number</t>
+  </si>
+  <si>
+    <t>tracknumber</t>
+  </si>
+  <si>
+    <t>track num/total tracks</t>
+  </si>
+  <si>
+    <t>WM/TrackNumber</t>
+  </si>
+  <si>
+    <t>Track Title</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>TIT2</t>
+  </si>
+  <si>
+    <t>©nam</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Track Title Sort Order [4]</t>
+  </si>
+  <si>
+    <t>titlesort</t>
+  </si>
+  <si>
+    <t>TSOT</t>
+  </si>
+  <si>
+    <t>sonm</t>
+  </si>
+  <si>
+    <t>WM/TitleSortOrder</t>
+  </si>
+  <si>
+    <t>Website (official artist website)</t>
+  </si>
+  <si>
+    <t>website</t>
+  </si>
+  <si>
+    <t>WOAR</t>
+  </si>
+  <si>
+    <t>WM/AuthorURL (Picard&gt;=1.3.1)</t>
+  </si>
+  <si>
+    <t>Work Title</t>
+  </si>
+  <si>
+    <t>work (Picard&gt;=1.3)</t>
+  </si>
+  <si>
+    <t>TXXX:WORK TIT1 [8]</t>
+  </si>
+  <si>
+    <t>©wrk (Picard&gt;=2.1)</t>
+  </si>
+  <si>
+    <t>WM/Work</t>
+  </si>
+  <si>
+    <t>Writer [2]</t>
+  </si>
+  <si>
+    <t>writer</t>
+  </si>
+  <si>
+    <t>TXXX:Writer (Picard&gt;=1.3)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1392,22 +1394,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1422,7 +1409,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1463,150 +1450,104 @@
     </fill>
   </fills>
   <borders count="4">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
-      <right style="thin"/>
-      <top style="double"/>
-      <bottom style="double"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
-      <right style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1665,47 +1606,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1713,12 +1670,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1747,7 +1704,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1768,7 +1725,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1819,7 +1776,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1837,34 +1794,33 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I94"/>
-  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="39.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="54.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="33.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="255.72"/>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="3" max="3" width="39.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="5" max="5" width="54.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="33.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" customWidth="1"/>
+    <col min="9" max="9" width="255.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1893,7 +1849,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -1912,11 +1868,11 @@
         <v>13</v>
       </c>
       <c r="H2" s="4"/>
-      <c r="I2" s="5" t="s">
+      <c r="I2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
@@ -1935,69 +1891,69 @@
         <v>19</v>
       </c>
       <c r="H3" s="4"/>
-      <c r="I3" s="5" t="s">
+      <c r="I3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" s="11" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>34</v>
       </c>
@@ -2016,11 +1972,11 @@
         <v>38</v>
       </c>
       <c r="H6" s="4"/>
-      <c r="I6" s="5" t="s">
+      <c r="I6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>40</v>
       </c>
@@ -2039,11 +1995,11 @@
         <v>44</v>
       </c>
       <c r="H7" s="4"/>
-      <c r="I7" s="5" t="s">
+      <c r="I7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>46</v>
       </c>
@@ -2062,40 +2018,40 @@
         <v>49</v>
       </c>
       <c r="H8" s="4"/>
-      <c r="I8" s="5" t="s">
+      <c r="I8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>57</v>
       </c>
@@ -2114,11 +2070,11 @@
         <v>61</v>
       </c>
       <c r="H10" s="4"/>
-      <c r="I10" s="5" t="s">
+      <c r="I10" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>63</v>
       </c>
@@ -2138,7 +2094,7 @@
       </c>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>68</v>
       </c>
@@ -2158,7 +2114,7 @@
       </c>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>72</v>
       </c>
@@ -2178,7 +2134,7 @@
       </c>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>77</v>
       </c>
@@ -2198,7 +2154,7 @@
       </c>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>82</v>
       </c>
@@ -2218,83 +2174,83 @@
       </c>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" s="11" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" s="14" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
+    <row r="17" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13" t="s">
+      <c r="D17" s="12"/>
+      <c r="E17" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="H17" s="13" t="s">
+      <c r="H17" s="12" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="18" s="11" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
+    <row r="18" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>103</v>
       </c>
@@ -2314,7 +2270,7 @@
       </c>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>108</v>
       </c>
@@ -2334,33 +2290,33 @@
       </c>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" s="11" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
+    <row r="21" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>118</v>
       </c>
@@ -2380,31 +2336,31 @@
       </c>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" s="11" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
+    <row r="23" spans="1:8" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10" t="s">
+      <c r="D23" s="9"/>
+      <c r="E23" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>129</v>
       </c>
@@ -2424,7 +2380,7 @@
       </c>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>134</v>
       </c>
@@ -2444,7 +2400,7 @@
       </c>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>139</v>
       </c>
@@ -2464,7 +2420,7 @@
       </c>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>143</v>
       </c>
@@ -2484,7 +2440,7 @@
       </c>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>148</v>
       </c>
@@ -2504,33 +2460,33 @@
       </c>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+    <row r="29" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="G29" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="H29" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>156</v>
       </c>
@@ -2550,7 +2506,7 @@
       </c>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>161</v>
       </c>
@@ -2570,7 +2526,7 @@
       </c>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>166</v>
       </c>
@@ -2590,7 +2546,7 @@
       </c>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>171</v>
       </c>
@@ -2610,7 +2566,7 @@
       </c>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>176</v>
       </c>
@@ -2630,7 +2586,7 @@
       </c>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>180</v>
       </c>
@@ -2650,7 +2606,7 @@
       </c>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>185</v>
       </c>
@@ -2670,33 +2626,33 @@
       </c>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" s="14" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="12" t="s">
+    <row r="37" spans="1:8" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E37" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="F37" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="G37" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="H37" s="13" t="s">
+      <c r="H37" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>196</v>
       </c>
@@ -2716,7 +2672,7 @@
       </c>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>201</v>
       </c>
@@ -2736,7 +2692,7 @@
       </c>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>206</v>
       </c>
@@ -2756,7 +2712,7 @@
       </c>
       <c r="H40" s="4"/>
     </row>
-    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>211</v>
       </c>
@@ -2776,7 +2732,7 @@
       </c>
       <c r="H41" s="4"/>
     </row>
-    <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>215</v>
       </c>
@@ -2796,7 +2752,7 @@
       </c>
       <c r="H42" s="4"/>
     </row>
-    <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>219</v>
       </c>
@@ -2816,7 +2772,7 @@
       </c>
       <c r="H43" s="4"/>
     </row>
-    <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>222</v>
       </c>
@@ -2836,7 +2792,7 @@
       </c>
       <c r="H44" s="4"/>
     </row>
-    <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>227</v>
       </c>
@@ -2856,7 +2812,7 @@
       </c>
       <c r="H45" s="4"/>
     </row>
-    <row r="46" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>232</v>
       </c>
@@ -2876,7 +2832,7 @@
       </c>
       <c r="H46" s="4"/>
     </row>
-    <row r="47" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>237</v>
       </c>
@@ -2896,7 +2852,7 @@
       </c>
       <c r="H47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>242</v>
       </c>
@@ -2916,7 +2872,7 @@
       </c>
       <c r="H48" s="4"/>
     </row>
-    <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>247</v>
       </c>
@@ -2936,7 +2892,7 @@
       </c>
       <c r="H49" s="4"/>
     </row>
-    <row r="50" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>252</v>
       </c>
@@ -2956,7 +2912,7 @@
       </c>
       <c r="H50" s="4"/>
     </row>
-    <row r="51" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>257</v>
       </c>
@@ -2976,7 +2932,7 @@
       </c>
       <c r="H51" s="4"/>
     </row>
-    <row r="52" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>262</v>
       </c>
@@ -2996,7 +2952,7 @@
       </c>
       <c r="H52" s="4"/>
     </row>
-    <row r="53" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>267</v>
       </c>
@@ -3016,7 +2972,7 @@
       </c>
       <c r="H53" s="4"/>
     </row>
-    <row r="54" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>272</v>
       </c>
@@ -3036,7 +2992,7 @@
       </c>
       <c r="H54" s="4"/>
     </row>
-    <row r="55" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>277</v>
       </c>
@@ -3056,7 +3012,7 @@
       </c>
       <c r="H55" s="4"/>
     </row>
-    <row r="56" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>281</v>
       </c>
@@ -3076,7 +3032,7 @@
       </c>
       <c r="H56" s="4"/>
     </row>
-    <row r="57" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>286</v>
       </c>
@@ -3096,7 +3052,7 @@
       </c>
       <c r="H57" s="4"/>
     </row>
-    <row r="58" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>290</v>
       </c>
@@ -3116,7 +3072,7 @@
       </c>
       <c r="H58" s="4"/>
     </row>
-    <row r="59" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>294</v>
       </c>
@@ -3136,14 +3092,14 @@
       </c>
       <c r="H59" s="4"/>
     </row>
-    <row r="60" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="15" t="s">
+    <row r="60" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A60" s="14" t="s">
         <v>298</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="C60" s="15" t="s">
         <v>300</v>
       </c>
       <c r="D60" s="4"/>
@@ -3156,31 +3112,31 @@
       </c>
       <c r="H60" s="4"/>
     </row>
-    <row r="61" s="14" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="12" t="s">
+    <row r="61" spans="1:8" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="B61" s="13" t="s">
+      <c r="B61" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="C61" s="17" t="s">
+      <c r="C61" s="16" t="s">
         <v>304</v>
       </c>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13" t="s">
+      <c r="D61" s="12"/>
+      <c r="E61" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="F61" s="13" t="s">
+      <c r="F61" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="G61" s="13" t="s">
+      <c r="G61" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="H61" s="13" t="s">
+      <c r="H61" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>307</v>
       </c>
@@ -3200,7 +3156,7 @@
       </c>
       <c r="H62" s="4"/>
     </row>
-    <row r="63" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>310</v>
       </c>
@@ -3220,7 +3176,7 @@
       </c>
       <c r="H63" s="4"/>
     </row>
-    <row r="64" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>313</v>
       </c>
@@ -3240,7 +3196,7 @@
       </c>
       <c r="H64" s="4"/>
     </row>
-    <row r="65" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>316</v>
       </c>
@@ -3260,7 +3216,7 @@
       </c>
       <c r="H65" s="4"/>
     </row>
-    <row r="66" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>321</v>
       </c>
@@ -3280,33 +3236,33 @@
       </c>
       <c r="H66" s="4"/>
     </row>
-    <row r="67" s="14" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="12" t="s">
+    <row r="67" spans="1:9" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B67" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="D67" s="13" t="s">
+      <c r="D67" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E67" s="13" t="s">
+      <c r="E67" s="12" t="s">
         <v>328</v>
       </c>
-      <c r="F67" s="13" t="s">
+      <c r="F67" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="G67" s="13" t="s">
+      <c r="G67" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="H67" s="13" t="s">
+      <c r="H67" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>330</v>
       </c>
@@ -3326,36 +3282,36 @@
       </c>
       <c r="H68" s="4"/>
     </row>
-    <row r="69" s="8" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6" t="s">
+    <row r="69" spans="1:9" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="C69" s="18" t="s">
+      <c r="C69" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="D69" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E69" s="7" t="s">
+      <c r="E69" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="F69" s="7" t="s">
+      <c r="F69" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G69" s="7" t="s">
+      <c r="G69" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="H69" s="7" t="s">
+      <c r="H69" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="I69" s="8" t="s">
+      <c r="I69" s="7" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>342</v>
       </c>
@@ -3375,7 +3331,7 @@
       </c>
       <c r="H70" s="4"/>
     </row>
-    <row r="71" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>347</v>
       </c>
@@ -3395,7 +3351,7 @@
       </c>
       <c r="H71" s="4"/>
     </row>
-    <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>352</v>
       </c>
@@ -3415,7 +3371,7 @@
       </c>
       <c r="H72" s="4"/>
     </row>
-    <row r="73" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>357</v>
       </c>
@@ -3435,7 +3391,7 @@
       </c>
       <c r="H73" s="4"/>
     </row>
-    <row r="74" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>362</v>
       </c>
@@ -3455,7 +3411,7 @@
       </c>
       <c r="H74" s="4"/>
     </row>
-    <row r="75" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>367</v>
       </c>
@@ -3475,7 +3431,7 @@
       </c>
       <c r="H75" s="4"/>
     </row>
-    <row r="76" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>372</v>
       </c>
@@ -3495,7 +3451,7 @@
       </c>
       <c r="H76" s="4"/>
     </row>
-    <row r="77" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>377</v>
       </c>
@@ -3515,7 +3471,7 @@
       </c>
       <c r="H77" s="4"/>
     </row>
-    <row r="78" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>382</v>
       </c>
@@ -3535,7 +3491,7 @@
       </c>
       <c r="H78" s="4"/>
     </row>
-    <row r="79" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>387</v>
       </c>
@@ -3555,7 +3511,7 @@
       </c>
       <c r="H79" s="4"/>
     </row>
-    <row r="80" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>392</v>
       </c>
@@ -3575,7 +3531,7 @@
       </c>
       <c r="H80" s="4"/>
     </row>
-    <row r="81" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>397</v>
       </c>
@@ -3595,7 +3551,7 @@
       </c>
       <c r="H81" s="4"/>
     </row>
-    <row r="82" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>400</v>
       </c>
@@ -3615,7 +3571,7 @@
       </c>
       <c r="H82" s="4"/>
     </row>
-    <row r="83" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>403</v>
       </c>
@@ -3635,7 +3591,7 @@
       </c>
       <c r="H83" s="4"/>
     </row>
-    <row r="84" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>407</v>
       </c>
@@ -3655,33 +3611,33 @@
       </c>
       <c r="H84" s="4"/>
     </row>
-    <row r="85" s="11" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="9" t="s">
+    <row r="85" spans="1:8" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A85" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B85" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="C85" s="10" t="s">
+      <c r="C85" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="D85" s="10" t="s">
+      <c r="D85" s="9" t="s">
         <v>414</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="E85" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="F85" s="10" t="s">
+      <c r="F85" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="G85" s="10" t="s">
+      <c r="G85" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="H85" s="10" t="s">
+      <c r="H85" s="9" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>417</v>
       </c>
@@ -3701,59 +3657,59 @@
       </c>
       <c r="H86" s="4"/>
     </row>
-    <row r="87" s="11" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="9" t="s">
+    <row r="87" spans="1:8" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A87" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="B87" s="10" t="s">
+      <c r="B87" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="C87" s="10" t="s">
+      <c r="C87" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="D87" s="10" t="s">
+      <c r="D87" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="E87" s="10" t="s">
+      <c r="E87" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="F87" s="10" t="s">
+      <c r="F87" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="G87" s="10" t="s">
+      <c r="G87" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="H87" s="10" t="s">
+      <c r="H87" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="88" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="6" t="s">
+    <row r="88" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B88" s="7" t="s">
+      <c r="B88" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="C88" s="7" t="s">
+      <c r="C88" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="D88" s="7" t="s">
+      <c r="D88" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E88" s="7" t="s">
+      <c r="E88" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="F88" s="7" t="s">
+      <c r="F88" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G88" s="7" t="s">
+      <c r="G88" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="H88" s="7" t="s">
+      <c r="H88" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>430</v>
       </c>
@@ -3773,7 +3729,7 @@
       </c>
       <c r="H89" s="4"/>
     </row>
-    <row r="90" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>435</v>
       </c>
@@ -3793,7 +3749,7 @@
       </c>
       <c r="H90" s="4"/>
     </row>
-    <row r="91" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>439</v>
       </c>
@@ -3813,7 +3769,7 @@
       </c>
       <c r="H91" s="4"/>
     </row>
-    <row r="92" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>444</v>
       </c>
@@ -3833,16 +3789,11 @@
       </c>
       <c r="H92" s="4"/>
     </row>
-    <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="19"/>
+    <row r="94" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B94" s="18"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>